--- a/06_ISTQB/EXAM/answer.xlsx
+++ b/06_ISTQB/EXAM/answer.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="7">
   <si>
     <t>Set A</t>
   </si>
@@ -38,15 +38,25 @@
   <si>
     <t>d</t>
   </si>
+  <si>
+    <t>Fehler 14</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -84,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -93,6 +103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -373,21 +384,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -395,7 +409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -403,7 +417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -411,7 +425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -419,15 +433,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -435,23 +452,29 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -459,15 +482,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C11" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -475,7 +501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -483,7 +509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -491,7 +517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -499,7 +525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -507,7 +533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -515,15 +541,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -531,7 +560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -539,15 +568,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -555,7 +587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -563,7 +595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -571,7 +603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -579,7 +611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -587,97 +619,150 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="3"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="3"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="3"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="3"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="3"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="3"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="3"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/06_ISTQB/EXAM/answer.xlsx
+++ b/06_ISTQB/EXAM/answer.xlsx
@@ -7,7 +7,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Set A" sheetId="1" r:id="rId1"/>
+    <sheet name="Set B" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="26">
   <si>
     <t>Set A</t>
   </si>
@@ -39,7 +40,64 @@
     <t>d</t>
   </si>
   <si>
-    <t>Fehler 14</t>
+    <t>Missverständnis der Frage</t>
+  </si>
+  <si>
+    <t>Missverständnis des Antwortes</t>
+  </si>
+  <si>
+    <t>Nicht völlig verstehen der Frage. Bitte ausführlich lesen.</t>
+  </si>
+  <si>
+    <t>GIVEN/WHEN/THEN: BDD (Behavioral Driven Development)</t>
+  </si>
+  <si>
+    <t>Fehler 15</t>
+  </si>
+  <si>
+    <t>Autor ist für Walkthrough zuständig.</t>
+  </si>
+  <si>
+    <t>Exploratives Testen</t>
+  </si>
+  <si>
+    <t>Bitte ausführlich lesen.</t>
+  </si>
+  <si>
+    <t>Bitte ausführlich lesen. Endkriterien</t>
+  </si>
+  <si>
+    <t>Set B</t>
+  </si>
+  <si>
+    <t>Moderator:</t>
+  </si>
+  <si>
+    <t>11:03:00 - 12: 18</t>
+  </si>
+  <si>
+    <t>Fehler: 12</t>
+  </si>
+  <si>
+    <t>inkrementellen Entwicklungsmodell vs. sequenzielles Entwicklungsmodell</t>
+  </si>
+  <si>
+    <t>Zweigtest: White-Box-test</t>
+  </si>
+  <si>
+    <t>3-Wert-Grenzwertanalyse: Grenzwerte und Nachbaren</t>
+  </si>
+  <si>
+    <t>statische Test bevor Code schreiben</t>
+  </si>
+  <si>
+    <t>Virtuelle Maschinen: Werkzeuge zur Unterstützung der Skalierbarkeit und Standardisierung der Bereitstellung</t>
+  </si>
+  <si>
+    <t>übersichtlich</t>
+  </si>
+  <si>
+    <t>Fehler: 5</t>
   </si>
 </sst>
 </file>
@@ -62,7 +120,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -81,6 +139,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -104,6 +168,19 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -384,13 +461,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="56.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -398,42 +478,60 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E1" s="9">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -443,16 +541,28 @@
       <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -462,8 +572,14 @@
       <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -473,16 +589,28 @@
       <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -492,56 +620,89 @@
       <c r="C11" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -551,24 +712,36 @@
       <c r="C18" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -578,56 +751,83 @@
       <c r="C21" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -637,24 +837,37 @@
       <c r="C28" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -664,8 +877,15 @@
       <c r="C31" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -675,24 +895,36 @@
       <c r="C32" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -700,18 +932,24 @@
         <v>4</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -721,16 +959,22 @@
       <c r="C37" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -738,8 +982,11 @@
       <c r="C39" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -749,8 +996,11 @@
       <c r="C40" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -758,11 +1008,442 @@
         <v>1</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="7"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="7"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
 </file>